--- a/data/trans_bre/P1804_2016_2023-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1804_2016_2023-Edad-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,26</t>
+          <t>7,47</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>806,85%</t>
+          <t>720,31%</t>
         </is>
       </c>
     </row>
@@ -601,17 +601,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 5,66</t>
+          <t>-2,02; 5,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 13,03</t>
+          <t>3,3; 12,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 116,21</t>
+          <t>-24,81; 105,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,13</t>
+          <t>3,36</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>43,41%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 8,55</t>
+          <t>2,87; 8,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 7,15</t>
+          <t>-2,27; 8,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,46; 242,23</t>
+          <t>48,64; 249,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,65; 153,49</t>
+          <t>-20,6; 165,6</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,11</t>
+          <t>3,27</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>69,39%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 7,94</t>
+          <t>2,54; 8,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 5,77</t>
+          <t>0,6; 5,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44,98; 282,26</t>
+          <t>46,51; 280,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 182,57</t>
+          <t>6,99; 183,84</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,56</t>
+          <t>-1,51; 3,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 5,51</t>
+          <t>-2,34; 3,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-24,29; 95,28</t>
+          <t>-24,45; 93,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 224,13</t>
+          <t>-26,51; 61,85</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,13</t>
+          <t>1,25</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 6,87</t>
+          <t>-1,05; 6,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 3,77</t>
+          <t>-1,35; 3,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 114,03</t>
+          <t>-11,81; 107,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 70,9</t>
+          <t>-16,01; 69,29</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-2,96</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-35,41%</t>
+          <t>-0,45%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 4,95</t>
+          <t>-4,27; 5,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 0,98</t>
+          <t>-3,09; 2,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,96; 57,86</t>
+          <t>-31,81; 66,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-74,59; 12,35</t>
+          <t>-31,04; 39,7</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>1,76</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 12,54</t>
+          <t>1,24; 12,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 4,42</t>
+          <t>-1,52; 4,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,96; 183,63</t>
+          <t>7,44; 179,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,35; 86,54</t>
+          <t>-17,19; 89,37</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2,05</t>
+          <t>2,34</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,81%</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,98</t>
+          <t>2,17; 4,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,76</t>
+          <t>1,07; 3,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33,36; 87,3</t>
+          <t>31,87; 88,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,0; 81,83</t>
+          <t>15,88; 64,21</t>
         </is>
       </c>
     </row>
